--- a/results/nhanes__age-x-race__routine-blood-tests/results.xlsx
+++ b/results/nhanes__age-x-race__routine-blood-tests/results.xlsx
@@ -24,15 +24,15 @@
     <sheet name="select" sheetId="15" r:id="rId15"/>
     <sheet name="select_picks_summary" sheetId="16" r:id="rId16"/>
     <sheet name="pareto" sheetId="17" r:id="rId17"/>
-    <sheet name="external" sheetId="18" r:id="rId18"/>
-    <sheet name="shap_by_group" sheetId="19" r:id="rId19"/>
+    <sheet name="shap_by_group" sheetId="18" r:id="rId18"/>
+    <sheet name="lime_shap_agreement" sheetId="19" r:id="rId19"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="450">
   <si>
     <t>Value</t>
   </si>
@@ -808,12 +808,18 @@
     <t>Reweighing (pre-processing)</t>
   </si>
   <si>
+    <t>Group-balanced SMOTE (pre-processing)</t>
+  </si>
+  <si>
     <t>Exponentiated Gradient (in-processing)</t>
   </si>
   <si>
     <t>Threshold Optimizer (post-processing)</t>
   </si>
   <si>
+    <t>Reject Option Classification (post-processing)</t>
+  </si>
+  <si>
     <t>Reweighing + Threshold Optimizer (hybrid)</t>
   </si>
   <si>
@@ -823,12 +829,18 @@
     <t>0.722 ± 0.001</t>
   </si>
   <si>
+    <t>0.710 ± 0.002</t>
+  </si>
+  <si>
     <t>0.677 ± 0.008</t>
   </si>
   <si>
     <t>0.733 ± 0.013</t>
   </si>
   <si>
+    <t>0.719 ± 0.006</t>
+  </si>
+  <si>
     <t>0.672 ± 0.026</t>
   </si>
   <si>
@@ -838,12 +850,18 @@
     <t>0.748 ± 0.007</t>
   </si>
   <si>
+    <t>0.819 ± 0.004</t>
+  </si>
+  <si>
     <t>0.781 ± 0.002</t>
   </si>
   <si>
     <t>0.702 ± 0.025</t>
   </si>
   <si>
+    <t>0.740 ± 0.007</t>
+  </si>
+  <si>
     <t>0.694 ± 0.045</t>
   </si>
   <si>
@@ -853,12 +871,18 @@
     <t>0.698 ± 0.001</t>
   </si>
   <si>
+    <t>0.690 ± 0.002</t>
+  </si>
+  <si>
     <t>0.641 ± 0.008</t>
   </si>
   <si>
     <t>0.623 ± 0.007</t>
   </si>
   <si>
+    <t>0.708 ± 0.004</t>
+  </si>
+  <si>
     <t>0.620 ± 0.007</t>
   </si>
   <si>
@@ -868,9 +892,15 @@
     <t>0.695 ± 0.007</t>
   </si>
   <si>
+    <t>0.680 ± 0.008</t>
+  </si>
+  <si>
     <t>0.615 ± 0.011</t>
   </si>
   <si>
+    <t>0.710 ± 0.005</t>
+  </si>
+  <si>
     <t>0.608 ± 0.004</t>
   </si>
   <si>
@@ -880,12 +910,18 @@
     <t>0.658 ± 0.003</t>
   </si>
   <si>
+    <t>0.659 ± 0.004</t>
+  </si>
+  <si>
     <t>0.585 ± 0.009</t>
   </si>
   <si>
     <t>0.447 ± 0.029</t>
   </si>
   <si>
+    <t>0.691 ± 0.004</t>
+  </si>
+  <si>
     <t>0.536 ± 0.050</t>
   </si>
   <si>
@@ -895,12 +931,18 @@
     <t>0.611 ± 0.010</t>
   </si>
   <si>
+    <t>0.459 ± 0.013</t>
+  </si>
+  <si>
     <t>0.559 ± 0.014</t>
   </si>
   <si>
     <t>0.476 ± 0.053</t>
   </si>
   <si>
+    <t>0.663 ± 0.006</t>
+  </si>
+  <si>
     <t>0.470 ± 0.065</t>
   </si>
   <si>
@@ -910,12 +952,18 @@
     <t>0.468 ± 0.001</t>
   </si>
   <si>
+    <t>0.457 ± 0.003</t>
+  </si>
+  <si>
     <t>0.402 ± 0.009</t>
   </si>
   <si>
     <t>0.383 ± 0.010</t>
   </si>
   <si>
+    <t>0.477 ± 0.006</t>
+  </si>
+  <si>
     <t>0.378 ± 0.008</t>
   </si>
   <si>
@@ -925,12 +973,18 @@
     <t>0.473 ± 0.010</t>
   </si>
   <si>
+    <t>0.484 ± 0.013</t>
+  </si>
+  <si>
     <t>0.487 ± 0.009</t>
   </si>
   <si>
     <t>0.372 ± 0.013</t>
   </si>
   <si>
+    <t>0.486 ± 0.007</t>
+  </si>
+  <si>
     <t>0.363 ± 0.004</t>
   </si>
   <si>
@@ -940,12 +994,18 @@
     <t>0.314 ± 0.003</t>
   </si>
   <si>
+    <t>0.259 ± 0.008</t>
+  </si>
+  <si>
     <t>0.097 ± 0.027</t>
   </si>
   <si>
     <t>0.104 ± 0.020</t>
   </si>
   <si>
+    <t>0.354 ± 0.009</t>
+  </si>
+  <si>
     <t>0.116 ± 0.021</t>
   </si>
   <si>
@@ -955,24 +1015,36 @@
     <t>0.260 ± 0.012</t>
   </si>
   <si>
+    <t>0.284 ± 0.007</t>
+  </si>
+  <si>
     <t>0.261 ± 0.008</t>
   </si>
   <si>
     <t>0.098 ± 0.017</t>
   </si>
   <si>
+    <t>0.337 ± 0.030</t>
+  </si>
+  <si>
     <t>0.196 ± 0.002</t>
   </si>
   <si>
     <t>0.402 ± 0.004</t>
   </si>
   <si>
+    <t>0.485 ± 0.011</t>
+  </si>
+  <si>
     <t>0.767 ± 0.058</t>
   </si>
   <si>
     <t>0.672 ± 0.034</t>
   </si>
   <si>
+    <t>0.387 ± 0.012</t>
+  </si>
+  <si>
     <t>0.718 ± 0.049</t>
   </si>
   <si>
@@ -982,12 +1054,18 @@
     <t>0.430 ± 0.020</t>
   </si>
   <si>
+    <t>0.224 ± 0.009</t>
+  </si>
+  <si>
     <t>0.350 ± 0.013</t>
   </si>
   <si>
     <t>0.718 ± 0.041</t>
   </si>
   <si>
+    <t>0.377 ± 0.040</t>
+  </si>
+  <si>
     <t>0.715 ± 0.068</t>
   </si>
   <si>
@@ -997,12 +1075,18 @@
     <t>0.293 ± 0.012</t>
   </si>
   <si>
+    <t>0.317 ± 0.020</t>
+  </si>
+  <si>
     <t>0.147 ± 0.027</t>
   </si>
   <si>
     <t>0.212 ± 0.058</t>
   </si>
   <si>
+    <t>0.388 ± 0.026</t>
+  </si>
+  <si>
     <t>0.171 ± 0.038</t>
   </si>
   <si>
@@ -1012,12 +1096,18 @@
     <t>0.299 ± 0.026</t>
   </si>
   <si>
+    <t>0.392 ± 0.022</t>
+  </si>
+  <si>
     <t>0.337 ± 0.040</t>
   </si>
   <si>
     <t>0.164 ± 0.056</t>
   </si>
   <si>
+    <t>0.386 ± 0.030</t>
+  </si>
+  <si>
     <t>0.234 ± 0.084</t>
   </si>
   <si>
@@ -1030,12 +1120,18 @@
     <t>0.392 ± 0.009</t>
   </si>
   <si>
+    <t>0.417 ± 0.015</t>
+  </si>
+  <si>
     <t>0.464 ± 0.016</t>
   </si>
   <si>
     <t>0.449 ± 0.018</t>
   </si>
   <si>
+    <t>0.431 ± 0.010</t>
+  </si>
+  <si>
     <t>0.417 ± 0.003</t>
   </si>
   <si>
@@ -1045,12 +1141,18 @@
     <t>0.508 ± 0.018</t>
   </si>
   <si>
+    <t>0.538 ± 0.022</t>
+  </si>
+  <si>
     <t>0.511 ± 0.015</t>
   </si>
   <si>
     <t>0.428 ± 0.020</t>
   </si>
   <si>
+    <t>0.498 ± 0.017</t>
+  </si>
+  <si>
     <t>0.430 ± 0.041</t>
   </si>
   <si>
@@ -1060,12 +1162,18 @@
     <t>0.188 ± 0.012</t>
   </si>
   <si>
+    <t>0.142 ± 0.017</t>
+  </si>
+  <si>
     <t>0.080 ± 0.015</t>
   </si>
   <si>
     <t>0.142 ± 0.027</t>
   </si>
   <si>
+    <t>0.175 ± 0.015</t>
+  </si>
+  <si>
     <t>0.084 ± 0.039</t>
   </si>
   <si>
@@ -1075,12 +1183,18 @@
     <t>0.143 ± 0.021</t>
   </si>
   <si>
+    <t>0.162 ± 0.016</t>
+  </si>
+  <si>
     <t>0.187 ± 0.026</t>
   </si>
   <si>
     <t>0.129 ± 0.020</t>
   </si>
   <si>
+    <t>0.178 ± 0.043</t>
+  </si>
+  <si>
     <t>0.136 ± 0.044</t>
   </si>
   <si>
@@ -1108,12 +1222,18 @@
     <t>Reweighing</t>
   </si>
   <si>
+    <t>SMOTE</t>
+  </si>
+  <si>
     <t>Exp. Gradient</t>
   </si>
   <si>
     <t>Threshold Opt.</t>
   </si>
   <si>
+    <t>Reject Option</t>
+  </si>
+  <si>
     <t>RW + TO (hybrid)</t>
   </si>
   <si>
@@ -1123,12 +1243,18 @@
     <t>[-0.467, -0.185]</t>
   </si>
   <si>
+    <t>[-0.462, -0.170]</t>
+  </si>
+  <si>
     <t>[-0.604, -0.286]</t>
   </si>
   <si>
     <t>[-0.625, -0.229]</t>
   </si>
   <si>
+    <t>[-0.390, -0.143]</t>
+  </si>
+  <si>
     <t>[-0.618, -0.261]</t>
   </si>
   <si>
@@ -1138,12 +1264,18 @@
     <t>[-0.447, -0.174]</t>
   </si>
   <si>
+    <t>[-0.381, -0.138]</t>
+  </si>
+  <si>
     <t>[-0.443, -0.193]</t>
   </si>
   <si>
     <t>[-0.578, -0.219]</t>
   </si>
   <si>
+    <t>[-0.353, -0.139]</t>
+  </si>
+  <si>
     <t>[-0.583, -0.204]</t>
   </si>
   <si>
@@ -1153,12 +1285,18 @@
     <t>[-0.055, -0.026]</t>
   </si>
   <si>
+    <t>[-0.059, -0.030]</t>
+  </si>
+  <si>
     <t>[-0.106, -0.069]</t>
   </si>
   <si>
     <t>[-0.123, -0.086]</t>
   </si>
   <si>
+    <t>[-0.046, -0.021]</t>
+  </si>
+  <si>
     <t>[-0.129, -0.093]</t>
   </si>
   <si>
@@ -1168,12 +1306,18 @@
     <t>[-0.055, -0.028]</t>
   </si>
   <si>
+    <t>[-0.070, -0.039]</t>
+  </si>
+  <si>
     <t>[-0.060, -0.030]</t>
   </si>
   <si>
     <t>[-0.135, -0.100]</t>
   </si>
   <si>
+    <t>[-0.035, -0.011]</t>
+  </si>
+  <si>
     <t>[-0.140, -0.103]</t>
   </si>
   <si>
@@ -1198,31 +1342,28 @@
     <t>Accuracy-driven selection</t>
   </si>
   <si>
-    <t>0.768 ± 0.005</t>
+    <t>0.731 ± 0.003</t>
   </si>
   <si>
     <t>0.761 ± 0.002</t>
   </si>
   <si>
-    <t>0.723 ± 0.002</t>
+    <t>0.711 ± 0.002</t>
   </si>
   <si>
     <t>0.734 ± 0.004</t>
   </si>
   <si>
-    <t>0.651 ± 0.002</t>
-  </si>
-  <si>
     <t>0.692 ± 0.006</t>
   </si>
   <si>
-    <t>0.484 ± 0.015</t>
+    <t>0.365 ± 0.005</t>
   </si>
   <si>
     <t>0.615 ± 0.010</t>
   </si>
   <si>
-    <t>0.443 ± 0.006</t>
+    <t>0.351 ± 0.008</t>
   </si>
   <si>
     <t>0.614 ± 0.011</t>
@@ -1235,6 +1376,12 @@
   </si>
   <si>
     <t>Overall</t>
+  </si>
+  <si>
+    <t>Mean top-5 overlap (of 5)</t>
+  </si>
+  <si>
+    <t>Mean LIME local R2</t>
   </si>
 </sst>
 </file>
@@ -5532,7 +5679,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:12">
@@ -5616,34 +5763,34 @@
         <v>256</v>
       </c>
       <c r="C3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F3" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="G3" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="H3" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="I3" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="J3" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="K3" t="s">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="L3" t="s">
-        <v>340</v>
+        <v>374</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -5651,34 +5798,34 @@
         <v>257</v>
       </c>
       <c r="C4" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E4" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="F4" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="G4" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="H4" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="I4" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="J4" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
       <c r="K4" t="s">
-        <v>331</v>
+        <v>361</v>
       </c>
       <c r="L4" t="s">
-        <v>341</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -5686,34 +5833,34 @@
         <v>258</v>
       </c>
       <c r="C5" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D5" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E5" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F5" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="G5" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="H5" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="I5" t="s">
-        <v>321</v>
+        <v>347</v>
       </c>
       <c r="J5" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="K5" t="s">
-        <v>332</v>
+        <v>362</v>
       </c>
       <c r="L5" t="s">
-        <v>342</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -5721,34 +5868,34 @@
         <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D6" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="F6" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="G6" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="H6" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="I6" t="s">
-        <v>322</v>
+        <v>348</v>
       </c>
       <c r="J6" t="s">
-        <v>322</v>
+        <v>359</v>
       </c>
       <c r="K6" t="s">
-        <v>333</v>
+        <v>363</v>
       </c>
       <c r="L6" t="s">
-        <v>343</v>
+        <v>377</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -5756,253 +5903,393 @@
         <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D7" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E7" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="F7" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="G7" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="H7" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="I7" t="s">
+        <v>349</v>
+      </c>
+      <c r="J7" t="s">
+        <v>349</v>
+      </c>
+      <c r="K7" t="s">
+        <v>364</v>
+      </c>
+      <c r="L7" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="B8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" t="s">
+        <v>282</v>
+      </c>
+      <c r="E8" t="s">
+        <v>295</v>
+      </c>
+      <c r="F8" t="s">
+        <v>309</v>
+      </c>
+      <c r="G8" t="s">
         <v>323</v>
       </c>
-      <c r="J7" t="s">
-        <v>323</v>
-      </c>
-      <c r="K7" t="s">
-        <v>334</v>
-      </c>
-      <c r="L7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" t="s">
-        <v>147</v>
-      </c>
       <c r="H8" t="s">
-        <v>155</v>
+        <v>336</v>
       </c>
       <c r="I8" t="s">
-        <v>163</v>
+        <v>350</v>
       </c>
       <c r="J8" t="s">
-        <v>163</v>
+        <v>350</v>
       </c>
       <c r="K8" t="s">
-        <v>172</v>
+        <v>365</v>
       </c>
       <c r="L8" t="s">
-        <v>179</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="B9" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C9" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E9" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F9" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="G9" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="H9" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="I9" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="J9" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="K9" t="s">
-        <v>335</v>
+        <v>366</v>
       </c>
       <c r="L9" t="s">
-        <v>345</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C10" t="s">
-        <v>267</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>286</v>
+        <v>112</v>
       </c>
       <c r="F10" t="s">
-        <v>296</v>
+        <v>119</v>
       </c>
       <c r="G10" t="s">
-        <v>306</v>
+        <v>147</v>
       </c>
       <c r="H10" t="s">
-        <v>315</v>
+        <v>155</v>
       </c>
       <c r="I10" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="J10" t="s">
-        <v>325</v>
+        <v>163</v>
       </c>
       <c r="K10" t="s">
-        <v>336</v>
+        <v>172</v>
       </c>
       <c r="L10" t="s">
-        <v>346</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D11" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="E11" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="F11" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="G11" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="H11" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="I11" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="J11" t="s">
-        <v>326</v>
+        <v>352</v>
       </c>
       <c r="K11" t="s">
-        <v>337</v>
+        <v>367</v>
       </c>
       <c r="L11" t="s">
-        <v>347</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="B12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D12" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E12" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F12" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="G12" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="H12" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="I12" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="J12" t="s">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="K12" t="s">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="L12" t="s">
-        <v>348</v>
+        <v>382</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" t="s">
+        <v>286</v>
+      </c>
+      <c r="E13" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13" t="s">
+        <v>313</v>
+      </c>
+      <c r="G13" t="s">
+        <v>327</v>
+      </c>
+      <c r="H13" t="s">
+        <v>340</v>
+      </c>
+      <c r="I13" t="s">
+        <v>354</v>
+      </c>
+      <c r="J13" t="s">
+        <v>354</v>
+      </c>
+      <c r="K13" t="s">
+        <v>369</v>
+      </c>
+      <c r="L13" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="B14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" t="s">
+        <v>273</v>
+      </c>
+      <c r="D14" t="s">
+        <v>285</v>
+      </c>
+      <c r="E14" t="s">
+        <v>300</v>
+      </c>
+      <c r="F14" t="s">
+        <v>314</v>
+      </c>
+      <c r="G14" t="s">
+        <v>328</v>
+      </c>
+      <c r="H14" t="s">
+        <v>341</v>
+      </c>
+      <c r="I14" t="s">
+        <v>355</v>
+      </c>
+      <c r="J14" t="s">
+        <v>355</v>
+      </c>
+      <c r="K14" t="s">
+        <v>370</v>
+      </c>
+      <c r="L14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="B15" t="s">
         <v>260</v>
       </c>
-      <c r="C13" t="s">
-        <v>270</v>
-      </c>
-      <c r="D13" t="s">
-        <v>279</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="C15" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E15" t="s">
+        <v>301</v>
+      </c>
+      <c r="F15" t="s">
+        <v>315</v>
+      </c>
+      <c r="G15" t="s">
+        <v>329</v>
+      </c>
+      <c r="H15" t="s">
+        <v>342</v>
+      </c>
+      <c r="I15" t="s">
+        <v>356</v>
+      </c>
+      <c r="J15" t="s">
+        <v>356</v>
+      </c>
+      <c r="K15" t="s">
+        <v>371</v>
+      </c>
+      <c r="L15" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="B16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" t="s">
+        <v>275</v>
+      </c>
+      <c r="D16" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" t="s">
+        <v>302</v>
+      </c>
+      <c r="F16" t="s">
+        <v>316</v>
+      </c>
+      <c r="G16" t="s">
+        <v>330</v>
+      </c>
+      <c r="H16" t="s">
+        <v>343</v>
+      </c>
+      <c r="I16" t="s">
+        <v>357</v>
+      </c>
+      <c r="J16" t="s">
+        <v>357</v>
+      </c>
+      <c r="K16" t="s">
+        <v>372</v>
+      </c>
+      <c r="L16" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" t="s">
+        <v>276</v>
+      </c>
+      <c r="D17" t="s">
         <v>289</v>
       </c>
-      <c r="F13" t="s">
-        <v>299</v>
-      </c>
-      <c r="G13" t="s">
-        <v>308</v>
-      </c>
-      <c r="H13" t="s">
-        <v>318</v>
-      </c>
-      <c r="I13" t="s">
-        <v>328</v>
-      </c>
-      <c r="J13" t="s">
-        <v>328</v>
-      </c>
-      <c r="K13" t="s">
-        <v>339</v>
-      </c>
-      <c r="L13" t="s">
-        <v>349</v>
+      <c r="E17" t="s">
+        <v>303</v>
+      </c>
+      <c r="F17" t="s">
+        <v>317</v>
+      </c>
+      <c r="G17" t="s">
+        <v>329</v>
+      </c>
+      <c r="H17" t="s">
+        <v>344</v>
+      </c>
+      <c r="I17" t="s">
+        <v>358</v>
+      </c>
+      <c r="J17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K17" t="s">
+        <v>373</v>
+      </c>
+      <c r="L17" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6010,7 +6297,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -6284,64 +6571,64 @@
         <v>258</v>
       </c>
       <c r="C5">
-        <v>0.66</v>
+        <v>0.781</v>
       </c>
       <c r="D5">
-        <v>0.269</v>
+        <v>0.384</v>
       </c>
       <c r="E5">
-        <v>0.576</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="F5">
-        <v>0.289</v>
+        <v>0.408</v>
       </c>
       <c r="G5">
-        <v>0.589</v>
+        <v>0.706</v>
       </c>
       <c r="H5">
-        <v>0.269</v>
+        <v>0.352</v>
       </c>
       <c r="I5">
-        <v>0.581</v>
+        <v>0.751</v>
       </c>
       <c r="J5">
-        <v>0.233</v>
+        <v>0.356</v>
       </c>
       <c r="K5">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="L5">
-        <v>0.296</v>
+        <v>0.33</v>
       </c>
       <c r="M5">
-        <v>0.5620000000000001</v>
+        <v>0.506</v>
       </c>
       <c r="N5">
-        <v>0.31</v>
+        <v>0.231</v>
       </c>
       <c r="O5">
-        <v>0.616</v>
+        <v>0.543</v>
       </c>
       <c r="P5">
-        <v>0.325</v>
+        <v>0.259</v>
       </c>
       <c r="Q5">
-        <v>0.553</v>
+        <v>0.463</v>
       </c>
       <c r="R5">
-        <v>0.357</v>
+        <v>0.277</v>
       </c>
       <c r="S5">
-        <v>0.53</v>
+        <v>0.509</v>
       </c>
       <c r="T5">
-        <v>0.3</v>
+        <v>0.221</v>
       </c>
       <c r="U5">
-        <v>0.583</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="V5">
-        <v>0.326</v>
+        <v>0.238</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -6349,64 +6636,64 @@
         <v>259</v>
       </c>
       <c r="C6">
-        <v>0.46</v>
+        <v>0.66</v>
       </c>
       <c r="D6">
-        <v>0.201</v>
+        <v>0.269</v>
       </c>
       <c r="E6">
-        <v>0.437</v>
+        <v>0.576</v>
       </c>
       <c r="F6">
-        <v>0.189</v>
+        <v>0.289</v>
       </c>
       <c r="G6">
-        <v>0.451</v>
+        <v>0.589</v>
       </c>
       <c r="H6">
-        <v>0.208</v>
+        <v>0.269</v>
       </c>
       <c r="I6">
-        <v>0.455</v>
+        <v>0.581</v>
       </c>
       <c r="J6">
-        <v>0.208</v>
+        <v>0.233</v>
       </c>
       <c r="K6">
-        <v>0.417</v>
+        <v>0.6</v>
       </c>
       <c r="L6">
-        <v>0.222</v>
+        <v>0.296</v>
       </c>
       <c r="M6">
-        <v>0.433</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="N6">
-        <v>0.197</v>
+        <v>0.31</v>
       </c>
       <c r="O6">
-        <v>0.42</v>
+        <v>0.616</v>
       </c>
       <c r="P6">
-        <v>0.22</v>
+        <v>0.325</v>
       </c>
       <c r="Q6">
-        <v>0.426</v>
+        <v>0.553</v>
       </c>
       <c r="R6">
-        <v>0.193</v>
+        <v>0.357</v>
       </c>
       <c r="S6">
-        <v>0.447</v>
+        <v>0.53</v>
       </c>
       <c r="T6">
-        <v>0.197</v>
+        <v>0.3</v>
       </c>
       <c r="U6">
-        <v>0.478</v>
+        <v>0.583</v>
       </c>
       <c r="V6">
-        <v>0.207</v>
+        <v>0.326</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -6414,463 +6701,723 @@
         <v>260</v>
       </c>
       <c r="C7">
-        <v>0.553</v>
+        <v>0.46</v>
       </c>
       <c r="D7">
-        <v>0.299</v>
+        <v>0.201</v>
       </c>
       <c r="E7">
-        <v>0.522</v>
+        <v>0.437</v>
       </c>
       <c r="F7">
-        <v>0.276</v>
+        <v>0.189</v>
       </c>
       <c r="G7">
-        <v>0.538</v>
+        <v>0.451</v>
       </c>
       <c r="H7">
-        <v>0.301</v>
+        <v>0.208</v>
       </c>
       <c r="I7">
-        <v>0.543</v>
+        <v>0.455</v>
       </c>
       <c r="J7">
-        <v>0.305</v>
+        <v>0.208</v>
       </c>
       <c r="K7">
-        <v>0.5580000000000001</v>
+        <v>0.417</v>
       </c>
       <c r="L7">
-        <v>0.296</v>
+        <v>0.222</v>
       </c>
       <c r="M7">
-        <v>0.534</v>
+        <v>0.433</v>
       </c>
       <c r="N7">
-        <v>0.293</v>
+        <v>0.197</v>
       </c>
       <c r="O7">
-        <v>0.535</v>
+        <v>0.42</v>
       </c>
       <c r="P7">
-        <v>0.302</v>
+        <v>0.22</v>
       </c>
       <c r="Q7">
-        <v>0.5</v>
+        <v>0.426</v>
       </c>
       <c r="R7">
-        <v>0.304</v>
+        <v>0.193</v>
       </c>
       <c r="S7">
-        <v>0.521</v>
+        <v>0.447</v>
       </c>
       <c r="T7">
-        <v>0.29</v>
+        <v>0.197</v>
       </c>
       <c r="U7">
-        <v>0.548</v>
+        <v>0.478</v>
       </c>
       <c r="V7">
-        <v>0.286</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="8" spans="1:22">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C8">
-        <v>0.8169999999999999</v>
+        <v>0.804</v>
       </c>
       <c r="D8">
-        <v>0.458</v>
+        <v>0.393</v>
       </c>
       <c r="E8">
-        <v>0.71</v>
+        <v>0.722</v>
       </c>
       <c r="F8">
-        <v>0.487</v>
+        <v>0.437</v>
       </c>
       <c r="G8">
-        <v>0.802</v>
+        <v>0.766</v>
       </c>
       <c r="H8">
-        <v>0.402</v>
+        <v>0.356</v>
       </c>
       <c r="I8">
-        <v>0.896</v>
+        <v>0.825</v>
       </c>
       <c r="J8">
-        <v>0.541</v>
+        <v>0.438</v>
       </c>
       <c r="K8">
-        <v>0.833</v>
+        <v>0.675</v>
       </c>
       <c r="L8">
-        <v>0.543</v>
+        <v>0.361</v>
       </c>
       <c r="M8">
-        <v>0.322</v>
+        <v>0.491</v>
       </c>
       <c r="N8">
-        <v>0.078</v>
+        <v>0.205</v>
       </c>
       <c r="O8">
-        <v>0.302</v>
+        <v>0.445</v>
       </c>
       <c r="P8">
-        <v>0.07099999999999999</v>
+        <v>0.229</v>
       </c>
       <c r="Q8">
-        <v>0.342</v>
+        <v>0.508</v>
       </c>
       <c r="R8">
-        <v>0.139</v>
+        <v>0.27</v>
       </c>
       <c r="S8">
-        <v>0.286</v>
+        <v>0.495</v>
       </c>
       <c r="T8">
-        <v>0.064</v>
+        <v>0.198</v>
       </c>
       <c r="U8">
-        <v>0.487</v>
+        <v>0.513</v>
       </c>
       <c r="V8">
-        <v>0.061</v>
+        <v>0.203</v>
       </c>
     </row>
     <row r="9" spans="1:22">
       <c r="B9" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C9">
-        <v>0.788</v>
+        <v>0.553</v>
       </c>
       <c r="D9">
-        <v>0.409</v>
+        <v>0.299</v>
       </c>
       <c r="E9">
-        <v>0.673</v>
+        <v>0.522</v>
       </c>
       <c r="F9">
-        <v>0.448</v>
+        <v>0.276</v>
       </c>
       <c r="G9">
-        <v>0.761</v>
+        <v>0.538</v>
       </c>
       <c r="H9">
-        <v>0.352</v>
+        <v>0.301</v>
       </c>
       <c r="I9">
-        <v>0.8139999999999999</v>
+        <v>0.543</v>
       </c>
       <c r="J9">
-        <v>0.41</v>
+        <v>0.305</v>
       </c>
       <c r="K9">
-        <v>0.758</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L9">
-        <v>0.443</v>
+        <v>0.296</v>
       </c>
       <c r="M9">
-        <v>0.385</v>
+        <v>0.534</v>
       </c>
       <c r="N9">
-        <v>0.108</v>
+        <v>0.293</v>
       </c>
       <c r="O9">
-        <v>0.351</v>
+        <v>0.535</v>
       </c>
       <c r="P9">
-        <v>0.103</v>
+        <v>0.302</v>
       </c>
       <c r="Q9">
-        <v>0.353</v>
+        <v>0.5</v>
       </c>
       <c r="R9">
-        <v>0.167</v>
+        <v>0.304</v>
       </c>
       <c r="S9">
-        <v>0.379</v>
+        <v>0.521</v>
       </c>
       <c r="T9">
-        <v>0.102</v>
+        <v>0.29</v>
       </c>
       <c r="U9">
-        <v>0.417</v>
+        <v>0.548</v>
       </c>
       <c r="V9">
-        <v>0.095</v>
+        <v>0.286</v>
       </c>
     </row>
     <row r="10" spans="1:22">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C10">
-        <v>0.662</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="D10">
-        <v>0.236</v>
+        <v>0.458</v>
       </c>
       <c r="E10">
-        <v>0.527</v>
+        <v>0.71</v>
       </c>
       <c r="F10">
-        <v>0.267</v>
+        <v>0.487</v>
       </c>
       <c r="G10">
-        <v>0.672</v>
+        <v>0.802</v>
       </c>
       <c r="H10">
-        <v>0.219</v>
+        <v>0.402</v>
       </c>
       <c r="I10">
-        <v>0.733</v>
+        <v>0.896</v>
       </c>
       <c r="J10">
-        <v>0.301</v>
+        <v>0.541</v>
       </c>
       <c r="K10">
-        <v>0.5580000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="L10">
-        <v>0.274</v>
+        <v>0.543</v>
       </c>
       <c r="M10">
-        <v>0.473</v>
+        <v>0.322</v>
       </c>
       <c r="N10">
-        <v>0.202</v>
+        <v>0.078</v>
       </c>
       <c r="O10">
-        <v>0.449</v>
+        <v>0.302</v>
       </c>
       <c r="P10">
-        <v>0.187</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Q10">
-        <v>0.458</v>
+        <v>0.342</v>
       </c>
       <c r="R10">
-        <v>0.262</v>
+        <v>0.139</v>
       </c>
       <c r="S10">
-        <v>0.456</v>
+        <v>0.286</v>
       </c>
       <c r="T10">
-        <v>0.177</v>
+        <v>0.064</v>
       </c>
       <c r="U10">
-        <v>0.583</v>
+        <v>0.487</v>
       </c>
       <c r="V10">
-        <v>0.176</v>
+        <v>0.061</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="B11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11">
-        <v>0.629</v>
+        <v>0.788</v>
       </c>
       <c r="D11">
-        <v>0.217</v>
+        <v>0.409</v>
       </c>
       <c r="E11">
-        <v>0.49</v>
+        <v>0.673</v>
       </c>
       <c r="F11">
-        <v>0.224</v>
+        <v>0.448</v>
       </c>
       <c r="G11">
-        <v>0.649</v>
+        <v>0.761</v>
       </c>
       <c r="H11">
-        <v>0.19</v>
+        <v>0.352</v>
       </c>
       <c r="I11">
-        <v>0.6840000000000001</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J11">
-        <v>0.241</v>
+        <v>0.41</v>
       </c>
       <c r="K11">
-        <v>0.5</v>
+        <v>0.758</v>
       </c>
       <c r="L11">
-        <v>0.265</v>
+        <v>0.443</v>
       </c>
       <c r="M11">
-        <v>0.392</v>
+        <v>0.385</v>
       </c>
       <c r="N11">
-        <v>0.139</v>
+        <v>0.108</v>
       </c>
       <c r="O11">
-        <v>0.367</v>
+        <v>0.351</v>
       </c>
       <c r="P11">
-        <v>0.144</v>
+        <v>0.103</v>
       </c>
       <c r="Q11">
-        <v>0.397</v>
+        <v>0.353</v>
       </c>
       <c r="R11">
-        <v>0.196</v>
+        <v>0.167</v>
       </c>
       <c r="S11">
-        <v>0.37</v>
+        <v>0.379</v>
       </c>
       <c r="T11">
-        <v>0.122</v>
+        <v>0.102</v>
       </c>
       <c r="U11">
-        <v>0.504</v>
+        <v>0.417</v>
       </c>
       <c r="V11">
-        <v>0.117</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="B12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C12">
-        <v>0.497</v>
+        <v>0.662</v>
       </c>
       <c r="D12">
-        <v>0.246</v>
+        <v>0.236</v>
       </c>
       <c r="E12">
-        <v>0.445</v>
+        <v>0.527</v>
       </c>
       <c r="F12">
-        <v>0.225</v>
+        <v>0.267</v>
       </c>
       <c r="G12">
-        <v>0.48</v>
+        <v>0.672</v>
       </c>
       <c r="H12">
-        <v>0.244</v>
+        <v>0.219</v>
       </c>
       <c r="I12">
-        <v>0.482</v>
+        <v>0.733</v>
       </c>
       <c r="J12">
-        <v>0.248</v>
+        <v>0.301</v>
       </c>
       <c r="K12">
-        <v>0.467</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="L12">
         <v>0.274</v>
       </c>
       <c r="M12">
-        <v>0.476</v>
+        <v>0.473</v>
       </c>
       <c r="N12">
-        <v>0.25</v>
+        <v>0.202</v>
       </c>
       <c r="O12">
-        <v>0.49</v>
+        <v>0.449</v>
       </c>
       <c r="P12">
-        <v>0.256</v>
+        <v>0.187</v>
       </c>
       <c r="Q12">
-        <v>0.421</v>
+        <v>0.458</v>
       </c>
       <c r="R12">
-        <v>0.253</v>
+        <v>0.262</v>
       </c>
       <c r="S12">
-        <v>0.474</v>
+        <v>0.456</v>
       </c>
       <c r="T12">
-        <v>0.239</v>
+        <v>0.177</v>
       </c>
       <c r="U12">
-        <v>0.53</v>
+        <v>0.583</v>
       </c>
       <c r="V12">
-        <v>0.241</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="B13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13">
+        <v>0.515</v>
+      </c>
+      <c r="D13">
+        <v>0.123</v>
+      </c>
+      <c r="E13">
+        <v>0.429</v>
+      </c>
+      <c r="F13">
+        <v>0.155</v>
+      </c>
+      <c r="G13">
+        <v>0.514</v>
+      </c>
+      <c r="H13">
+        <v>0.104</v>
+      </c>
+      <c r="I13">
+        <v>0.623</v>
+      </c>
+      <c r="J13">
+        <v>0.22</v>
+      </c>
+      <c r="K13">
+        <v>0.458</v>
+      </c>
+      <c r="L13">
+        <v>0.143</v>
+      </c>
+      <c r="M13">
+        <v>0.235</v>
+      </c>
+      <c r="N13">
+        <v>0.068</v>
+      </c>
+      <c r="O13">
+        <v>0.282</v>
+      </c>
+      <c r="P13">
+        <v>0.066</v>
+      </c>
+      <c r="Q13">
+        <v>0.297</v>
+      </c>
+      <c r="R13">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="S13">
+        <v>0.253</v>
+      </c>
+      <c r="T13">
+        <v>0.073</v>
+      </c>
+      <c r="U13">
+        <v>0.33</v>
+      </c>
+      <c r="V13">
+        <v>0.062</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="B14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14">
+        <v>0.629</v>
+      </c>
+      <c r="D14">
+        <v>0.217</v>
+      </c>
+      <c r="E14">
+        <v>0.49</v>
+      </c>
+      <c r="F14">
+        <v>0.224</v>
+      </c>
+      <c r="G14">
+        <v>0.649</v>
+      </c>
+      <c r="H14">
+        <v>0.19</v>
+      </c>
+      <c r="I14">
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="J14">
+        <v>0.241</v>
+      </c>
+      <c r="K14">
+        <v>0.5</v>
+      </c>
+      <c r="L14">
+        <v>0.265</v>
+      </c>
+      <c r="M14">
+        <v>0.392</v>
+      </c>
+      <c r="N14">
+        <v>0.139</v>
+      </c>
+      <c r="O14">
+        <v>0.367</v>
+      </c>
+      <c r="P14">
+        <v>0.144</v>
+      </c>
+      <c r="Q14">
+        <v>0.397</v>
+      </c>
+      <c r="R14">
+        <v>0.196</v>
+      </c>
+      <c r="S14">
+        <v>0.37</v>
+      </c>
+      <c r="T14">
+        <v>0.122</v>
+      </c>
+      <c r="U14">
+        <v>0.504</v>
+      </c>
+      <c r="V14">
+        <v>0.117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="B15" t="s">
         <v>260</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.497</v>
+      </c>
+      <c r="D15">
+        <v>0.246</v>
+      </c>
+      <c r="E15">
+        <v>0.445</v>
+      </c>
+      <c r="F15">
+        <v>0.225</v>
+      </c>
+      <c r="G15">
+        <v>0.48</v>
+      </c>
+      <c r="H15">
+        <v>0.244</v>
+      </c>
+      <c r="I15">
+        <v>0.482</v>
+      </c>
+      <c r="J15">
+        <v>0.248</v>
+      </c>
+      <c r="K15">
+        <v>0.467</v>
+      </c>
+      <c r="L15">
+        <v>0.274</v>
+      </c>
+      <c r="M15">
+        <v>0.476</v>
+      </c>
+      <c r="N15">
+        <v>0.25</v>
+      </c>
+      <c r="O15">
+        <v>0.49</v>
+      </c>
+      <c r="P15">
+        <v>0.256</v>
+      </c>
+      <c r="Q15">
+        <v>0.421</v>
+      </c>
+      <c r="R15">
+        <v>0.253</v>
+      </c>
+      <c r="S15">
+        <v>0.474</v>
+      </c>
+      <c r="T15">
+        <v>0.239</v>
+      </c>
+      <c r="U15">
+        <v>0.53</v>
+      </c>
+      <c r="V15">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="B16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16">
+        <v>0.74</v>
+      </c>
+      <c r="D16">
+        <v>0.311</v>
+      </c>
+      <c r="E16">
+        <v>0.58</v>
+      </c>
+      <c r="F16">
+        <v>0.343</v>
+      </c>
+      <c r="G16">
+        <v>0.725</v>
+      </c>
+      <c r="H16">
+        <v>0.251</v>
+      </c>
+      <c r="I16">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="J16">
+        <v>0.384</v>
+      </c>
+      <c r="K16">
+        <v>0.7</v>
+      </c>
+      <c r="L16">
+        <v>0.37</v>
+      </c>
+      <c r="M16">
+        <v>0.491</v>
+      </c>
+      <c r="N16">
+        <v>0.191</v>
+      </c>
+      <c r="O16">
+        <v>0.449</v>
+      </c>
+      <c r="P16">
+        <v>0.197</v>
+      </c>
+      <c r="Q16">
+        <v>0.468</v>
+      </c>
+      <c r="R16">
+        <v>0.273</v>
+      </c>
+      <c r="S16">
+        <v>0.456</v>
+      </c>
+      <c r="T16">
+        <v>0.18</v>
+      </c>
+      <c r="U16">
+        <v>0.635</v>
+      </c>
+      <c r="V16">
+        <v>0.179</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22">
+      <c r="B17" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17">
         <v>0.485</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.252</v>
       </c>
-      <c r="E13">
+      <c r="E17">
         <v>0.473</v>
       </c>
-      <c r="F13">
+      <c r="F17">
         <v>0.249</v>
       </c>
-      <c r="G13">
+      <c r="G17">
         <v>0.47</v>
       </c>
-      <c r="H13">
+      <c r="H17">
         <v>0.255</v>
       </c>
-      <c r="I13">
+      <c r="I17">
         <v>0.481</v>
       </c>
-      <c r="J13">
+      <c r="J17">
         <v>0.258</v>
       </c>
-      <c r="K13">
+      <c r="K17">
         <v>0.433</v>
       </c>
-      <c r="L13">
+      <c r="L17">
         <v>0.243</v>
       </c>
-      <c r="M13">
+      <c r="M17">
         <v>0.446</v>
       </c>
-      <c r="N13">
+      <c r="N17">
         <v>0.256</v>
       </c>
-      <c r="O13">
+      <c r="O17">
         <v>0.445</v>
       </c>
-      <c r="P13">
+      <c r="P17">
         <v>0.251</v>
       </c>
-      <c r="Q13">
+      <c r="Q17">
         <v>0.418</v>
       </c>
-      <c r="R13">
+      <c r="R17">
         <v>0.264</v>
       </c>
-      <c r="S13">
+      <c r="S17">
         <v>0.484</v>
       </c>
-      <c r="T13">
+      <c r="T17">
         <v>0.252</v>
       </c>
-      <c r="U13">
+      <c r="U17">
         <v>0.539</v>
       </c>
-      <c r="V13">
+      <c r="V17">
         <v>0.239</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6878,7 +7425,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6889,22 +7436,22 @@
         <v>254</v>
       </c>
       <c r="D1" t="s">
-        <v>350</v>
+        <v>388</v>
       </c>
       <c r="E1" t="s">
-        <v>351</v>
+        <v>389</v>
       </c>
       <c r="F1" t="s">
-        <v>352</v>
+        <v>390</v>
       </c>
       <c r="G1" t="s">
-        <v>353</v>
+        <v>391</v>
       </c>
       <c r="H1" t="s">
-        <v>354</v>
+        <v>392</v>
       </c>
       <c r="I1" t="s">
-        <v>355</v>
+        <v>393</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6915,13 +7462,13 @@
         <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>394</v>
       </c>
       <c r="D2">
         <v>-0.099</v>
       </c>
       <c r="E2" t="s">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="F2">
         <v>0.03</v>
@@ -6930,7 +7477,7 @@
         <v>-0.008</v>
       </c>
       <c r="H2" t="s">
-        <v>371</v>
+        <v>415</v>
       </c>
       <c r="I2">
         <v>0.066</v>
@@ -6944,13 +7491,13 @@
         <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="D3">
         <v>-0.314</v>
       </c>
       <c r="E3" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -6959,7 +7506,7 @@
         <v>-0.04</v>
       </c>
       <c r="H3" t="s">
-        <v>372</v>
+        <v>416</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6973,22 +7520,22 @@
         <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>396</v>
       </c>
       <c r="D4">
-        <v>-0.442</v>
+        <v>-0.308</v>
       </c>
       <c r="E4" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>-0.08699999999999999</v>
+        <v>-0.044</v>
       </c>
       <c r="H4" t="s">
-        <v>373</v>
+        <v>417</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7002,22 +7549,22 @@
         <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>397</v>
       </c>
       <c r="D5">
-        <v>-0.44</v>
+        <v>-0.442</v>
       </c>
       <c r="E5" t="s">
-        <v>364</v>
+        <v>404</v>
       </c>
       <c r="F5">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>-0.104</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="H5" t="s">
-        <v>374</v>
+        <v>418</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7031,22 +7578,22 @@
         <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>360</v>
+        <v>398</v>
       </c>
       <c r="D6">
-        <v>-0.441</v>
+        <v>-0.44</v>
       </c>
       <c r="E6" t="s">
-        <v>365</v>
+        <v>405</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="G6">
-        <v>-0.111</v>
+        <v>-0.104</v>
       </c>
       <c r="H6" t="s">
-        <v>375</v>
+        <v>419</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7057,28 +7604,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="D7">
-        <v>-0.113</v>
+        <v>-0.25</v>
       </c>
       <c r="E7" t="s">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="F7">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>-0.01</v>
+        <v>-0.034</v>
       </c>
       <c r="H7" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="I7">
-        <v>0.092</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -7086,25 +7633,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="D8">
-        <v>-0.318</v>
+        <v>-0.441</v>
       </c>
       <c r="E8" t="s">
-        <v>367</v>
+        <v>407</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8">
-        <v>-0.042</v>
+        <v>-0.111</v>
       </c>
       <c r="H8" t="s">
-        <v>377</v>
+        <v>421</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7118,25 +7665,25 @@
         <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>358</v>
+        <v>394</v>
       </c>
       <c r="D9">
-        <v>-0.312</v>
+        <v>-0.113</v>
       </c>
       <c r="E9" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G9">
-        <v>-0.045</v>
+        <v>-0.01</v>
       </c>
       <c r="H9" t="s">
-        <v>378</v>
+        <v>422</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -7147,22 +7694,22 @@
         <v>91</v>
       </c>
       <c r="C10" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="D10">
-        <v>-0.402</v>
+        <v>-0.318</v>
       </c>
       <c r="E10" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
       <c r="G10">
-        <v>-0.118</v>
+        <v>-0.042</v>
       </c>
       <c r="H10" t="s">
-        <v>379</v>
+        <v>423</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7176,24 +7723,140 @@
         <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>360</v>
+        <v>396</v>
       </c>
       <c r="D11">
+        <v>-0.255</v>
+      </c>
+      <c r="E11" t="s">
+        <v>410</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>-0.054</v>
+      </c>
+      <c r="H11" t="s">
+        <v>424</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" t="s">
+        <v>397</v>
+      </c>
+      <c r="D12">
+        <v>-0.312</v>
+      </c>
+      <c r="E12" t="s">
+        <v>411</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>-0.045</v>
+      </c>
+      <c r="H12" t="s">
+        <v>425</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" t="s">
+        <v>398</v>
+      </c>
+      <c r="D13">
+        <v>-0.402</v>
+      </c>
+      <c r="E13" t="s">
+        <v>412</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>-0.118</v>
+      </c>
+      <c r="H13" t="s">
+        <v>426</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14" t="s">
+        <v>399</v>
+      </c>
+      <c r="D14">
+        <v>-0.24</v>
+      </c>
+      <c r="E14" t="s">
+        <v>413</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>-0.023</v>
+      </c>
+      <c r="H14" t="s">
+        <v>427</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>400</v>
+      </c>
+      <c r="D15">
         <v>-0.4</v>
       </c>
-      <c r="E11" t="s">
-        <v>370</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="E15" t="s">
+        <v>414</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
         <v>-0.121</v>
       </c>
-      <c r="H11" t="s">
-        <v>380</v>
-      </c>
-      <c r="I11">
+      <c r="H15" t="s">
+        <v>428</v>
+      </c>
+      <c r="I15">
         <v>0</v>
       </c>
     </row>
@@ -7209,13 +7872,13 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="B1" t="s">
-        <v>381</v>
+        <v>429</v>
       </c>
       <c r="C1" t="s">
-        <v>382</v>
+        <v>430</v>
       </c>
       <c r="D1" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="E1" t="s">
         <v>230</v>
@@ -7224,10 +7887,10 @@
         <v>254</v>
       </c>
       <c r="G1" t="s">
-        <v>384</v>
+        <v>432</v>
       </c>
       <c r="H1" t="s">
-        <v>385</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -7241,19 +7904,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G2">
-        <v>0.719</v>
+        <v>0.711</v>
       </c>
       <c r="H2">
-        <v>0.447</v>
+        <v>0.422</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -7267,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E3" t="s">
         <v>85</v>
@@ -7293,19 +7956,19 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G4">
-        <v>0.721</v>
+        <v>0.709</v>
       </c>
       <c r="H4">
-        <v>0.466</v>
+        <v>0.465</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -7319,7 +7982,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E5" t="s">
         <v>85</v>
@@ -7345,19 +8008,19 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G6">
-        <v>0.714</v>
+        <v>0.706</v>
       </c>
       <c r="H6">
-        <v>0.533</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -7371,7 +8034,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E7" t="s">
         <v>91</v>
@@ -7397,19 +8060,19 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E8" t="s">
         <v>91</v>
       </c>
       <c r="F8" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G8">
-        <v>0.722</v>
+        <v>0.717</v>
       </c>
       <c r="H8">
-        <v>0.451</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -7423,7 +8086,7 @@
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E9" t="s">
         <v>91</v>
@@ -7449,19 +8112,19 @@
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E10" t="s">
         <v>91</v>
       </c>
       <c r="F10" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G10">
-        <v>0.717</v>
+        <v>0.713</v>
       </c>
       <c r="H10">
-        <v>0.488</v>
+        <v>0.483</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -7475,7 +8138,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E11" t="s">
         <v>85</v>
@@ -7501,19 +8164,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E12" t="s">
         <v>91</v>
       </c>
       <c r="F12" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G12">
-        <v>0.732</v>
+        <v>0.713</v>
       </c>
       <c r="H12">
-        <v>0.51</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -7527,7 +8190,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E13" t="s">
         <v>91</v>
@@ -7553,19 +8216,19 @@
         <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E14" t="s">
         <v>91</v>
       </c>
       <c r="F14" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G14">
-        <v>0.726</v>
+        <v>0.716</v>
       </c>
       <c r="H14">
-        <v>0.467</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -7579,7 +8242,7 @@
         <v>2</v>
       </c>
       <c r="D15" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E15" t="s">
         <v>85</v>
@@ -7605,19 +8268,19 @@
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E16" t="s">
         <v>91</v>
       </c>
       <c r="F16" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G16">
-        <v>0.716</v>
+        <v>0.711</v>
       </c>
       <c r="H16">
-        <v>0.546</v>
+        <v>0.416</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -7631,7 +8294,7 @@
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E17" t="s">
         <v>85</v>
@@ -7657,19 +8320,19 @@
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E18" t="s">
         <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G18">
-        <v>0.723</v>
+        <v>0.714</v>
       </c>
       <c r="H18">
-        <v>0.472</v>
+        <v>0.376</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -7683,7 +8346,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E19" t="s">
         <v>85</v>
@@ -7709,19 +8372,19 @@
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="E20" t="s">
         <v>85</v>
       </c>
       <c r="F20" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="G20">
-        <v>0.727</v>
+        <v>0.707</v>
       </c>
       <c r="H20">
-        <v>0.547</v>
+        <v>0.431</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -7735,7 +8398,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="E21" t="s">
         <v>91</v>
@@ -7762,7 +8425,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>383</v>
+        <v>431</v>
       </c>
       <c r="B1" t="s">
         <v>79</v>
@@ -7785,48 +8448,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>386</v>
+        <v>434</v>
       </c>
       <c r="B2" t="s">
-        <v>388</v>
+        <v>436</v>
       </c>
       <c r="C2" t="s">
-        <v>390</v>
+        <v>438</v>
       </c>
       <c r="D2" t="s">
-        <v>392</v>
+        <v>286</v>
       </c>
       <c r="E2" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
       <c r="F2" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
       <c r="G2" t="s">
-        <v>396</v>
+        <v>443</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>387</v>
+        <v>435</v>
       </c>
       <c r="B3" t="s">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="C3" t="s">
-        <v>391</v>
+        <v>439</v>
       </c>
       <c r="D3" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="E3" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="F3" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="G3" t="s">
-        <v>397</v>
+        <v>444</v>
       </c>
     </row>
   </sheetData>
@@ -7847,7 +8510,7 @@
         <v>254</v>
       </c>
       <c r="D1" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7858,10 +8521,10 @@
         <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7872,10 +8535,10 @@
         <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7885,7 +8548,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -7902,7 +8565,7 @@
         <v>137</v>
       </c>
       <c r="E1" t="s">
-        <v>399</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -7955,13 +8618,13 @@
         <v>258</v>
       </c>
       <c r="C5">
-        <v>0.641</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D5">
-        <v>0.155</v>
+        <v>0.317</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7969,13 +8632,13 @@
         <v>259</v>
       </c>
       <c r="C6">
-        <v>0.623</v>
+        <v>0.641</v>
       </c>
       <c r="D6">
-        <v>0.212</v>
+        <v>0.155</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -7983,27 +8646,24 @@
         <v>260</v>
       </c>
       <c r="C7">
-        <v>0.62</v>
+        <v>0.623</v>
       </c>
       <c r="D7">
-        <v>0.171</v>
+        <v>0.212</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>91</v>
-      </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C8">
-        <v>0.734</v>
+        <v>0.708</v>
       </c>
       <c r="D8">
-        <v>0.627</v>
+        <v>0.388</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -8011,27 +8671,30 @@
     </row>
     <row r="9" spans="1:5">
       <c r="B9" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="C9">
-        <v>0.722</v>
+        <v>0.62</v>
       </c>
       <c r="D9">
-        <v>0.473</v>
+        <v>0.171</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>91</v>
+      </c>
       <c r="B10" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C10">
-        <v>0.695</v>
+        <v>0.734</v>
       </c>
       <c r="D10">
-        <v>0.299</v>
+        <v>0.627</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -8039,27 +8702,27 @@
     </row>
     <row r="11" spans="1:5">
       <c r="B11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11">
-        <v>0.695</v>
+        <v>0.722</v>
       </c>
       <c r="D11">
-        <v>0.337</v>
+        <v>0.473</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="B12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C12">
-        <v>0.615</v>
+        <v>0.695</v>
       </c>
       <c r="D12">
-        <v>0.164</v>
+        <v>0.299</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -8067,22 +8730,78 @@
     </row>
     <row r="13" spans="1:5">
       <c r="B13" t="s">
+        <v>258</v>
+      </c>
+      <c r="C13">
+        <v>0.68</v>
+      </c>
+      <c r="D13">
+        <v>0.392</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="B14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14">
+        <v>0.695</v>
+      </c>
+      <c r="D14">
+        <v>0.337</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="B15" t="s">
         <v>260</v>
       </c>
-      <c r="C13">
+      <c r="C15">
+        <v>0.615</v>
+      </c>
+      <c r="D15">
+        <v>0.164</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="B16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16">
+        <v>0.71</v>
+      </c>
+      <c r="D16">
+        <v>0.386</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17">
         <v>0.608</v>
       </c>
-      <c r="D13">
+      <c r="D17">
         <v>0.234</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E17" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A2:A9"/>
+    <mergeCell ref="A10:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8090,641 +8809,688 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:12">
       <c r="B1" t="s">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>254</v>
+        <v>21</v>
       </c>
       <c r="D1" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="H1" t="s">
-        <v>136</v>
+        <v>26</v>
       </c>
       <c r="I1" t="s">
-        <v>137</v>
+        <v>27</v>
       </c>
       <c r="J1" t="s">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="K1" t="s">
-        <v>185</v>
+        <v>29</v>
       </c>
       <c r="L1" t="s">
-        <v>190</v>
-      </c>
-      <c r="M1" t="s">
-        <v>195</v>
-      </c>
-      <c r="N1" t="s">
-        <v>200</v>
-      </c>
-      <c r="O1" t="s">
-        <v>205</v>
-      </c>
-      <c r="P1" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>215</v>
-      </c>
-      <c r="R1" t="s">
-        <v>220</v>
-      </c>
-      <c r="S1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C2" t="s">
-        <v>255</v>
+        <v>447</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2">
+        <v>0.3815999925136566</v>
+      </c>
+      <c r="C2">
+        <v>0.4383000135421753</v>
       </c>
       <c r="D2">
-        <v>0.784</v>
+        <v>0.455700010061264</v>
       </c>
       <c r="E2">
-        <v>0.749</v>
+        <v>0.6923999786376953</v>
       </c>
       <c r="F2">
-        <v>0.696</v>
+        <v>0.4855999946594238</v>
       </c>
       <c r="G2">
-        <v>0.8070000000000001</v>
+        <v>0.4767999947071075</v>
       </c>
       <c r="H2">
-        <v>0.679</v>
+        <v>0.4833000004291534</v>
       </c>
       <c r="I2">
-        <v>0.679</v>
+        <v>0.4679000079631805</v>
       </c>
       <c r="J2">
-        <v>0.867</v>
+        <v>0.4866000115871429</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0.4801999926567078</v>
       </c>
       <c r="L2">
-        <v>0.85</v>
-      </c>
-      <c r="M2">
-        <v>0.886</v>
-      </c>
-      <c r="N2">
-        <v>0.625</v>
-      </c>
-      <c r="O2">
-        <v>0.394</v>
-      </c>
-      <c r="P2">
-        <v>0.344</v>
-      </c>
-      <c r="Q2">
-        <v>0.458</v>
-      </c>
-      <c r="R2">
-        <v>0.321</v>
-      </c>
-      <c r="S2">
-        <v>0.538</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C3" t="s">
-        <v>357</v>
+        <v>0.5005999803543091</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3">
+        <v>0.4943000078201294</v>
+      </c>
+      <c r="C3">
+        <v>0.4253000020980835</v>
       </c>
       <c r="D3">
-        <v>0.743</v>
+        <v>0.580299973487854</v>
       </c>
       <c r="E3">
-        <v>0.707</v>
+        <v>0.6037999987602234</v>
       </c>
       <c r="F3">
-        <v>0.655</v>
+        <v>0.4323999881744385</v>
       </c>
       <c r="G3">
-        <v>0.755</v>
+        <v>0.3041999936103821</v>
       </c>
       <c r="H3">
-        <v>0.488</v>
+        <v>0.3091000020503998</v>
       </c>
       <c r="I3">
-        <v>0.488</v>
+        <v>0.3553000092506409</v>
       </c>
       <c r="J3">
-        <v>0.762</v>
+        <v>0.3264999985694885</v>
       </c>
       <c r="K3">
-        <v>0.8</v>
+        <v>0.3519999980926514</v>
       </c>
       <c r="L3">
-        <v>0.725</v>
-      </c>
-      <c r="M3">
-        <v>0.695</v>
-      </c>
-      <c r="N3">
-        <v>0.312</v>
-      </c>
-      <c r="O3">
-        <v>0.586</v>
-      </c>
-      <c r="P3">
-        <v>0.5</v>
-      </c>
-      <c r="Q3">
-        <v>0.625</v>
-      </c>
-      <c r="R3">
-        <v>0.436</v>
-      </c>
-      <c r="S3">
-        <v>0.615</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" t="s">
-        <v>358</v>
+        <v>0.4066999852657318</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4">
+        <v>0.2639999985694885</v>
+      </c>
+      <c r="C4">
+        <v>0.2630000114440918</v>
       </c>
       <c r="D4">
-        <v>0.6860000000000001</v>
+        <v>0.3093000054359436</v>
       </c>
       <c r="E4">
-        <v>0.654</v>
+        <v>0.2517000138759613</v>
       </c>
       <c r="F4">
-        <v>0.608</v>
+        <v>0.2382999956607819</v>
       </c>
       <c r="G4">
-        <v>0.708</v>
+        <v>0.226500004529953</v>
       </c>
       <c r="H4">
-        <v>0.387</v>
+        <v>0.214599996805191</v>
       </c>
       <c r="I4">
-        <v>0.387</v>
+        <v>0.2395000010728836</v>
       </c>
       <c r="J4">
-        <v>0.636</v>
+        <v>0.2134000062942505</v>
       </c>
       <c r="K4">
-        <v>0.7</v>
+        <v>0.2337000072002411</v>
       </c>
       <c r="L4">
-        <v>0.608</v>
-      </c>
-      <c r="M4">
-        <v>0.589</v>
-      </c>
-      <c r="N4">
-        <v>0.312</v>
-      </c>
-      <c r="O4">
-        <v>0.636</v>
-      </c>
-      <c r="P4">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="Q4">
-        <v>0.667</v>
-      </c>
-      <c r="R4">
-        <v>0.487</v>
-      </c>
-      <c r="S4">
-        <v>0.6919999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" t="s">
-        <v>359</v>
+        <v>0.2398000061511993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5">
+        <v>0.2427999973297119</v>
+      </c>
+      <c r="C5">
+        <v>0.2456000000238419</v>
       </c>
       <c r="D5">
-        <v>0.8090000000000001</v>
+        <v>0.301800012588501</v>
       </c>
       <c r="E5">
-        <v>0.644</v>
+        <v>0.2720000147819519</v>
       </c>
       <c r="F5">
-        <v>0.4</v>
+        <v>0.2520000040531158</v>
+      </c>
+      <c r="G5">
+        <v>0.2072000056505203</v>
       </c>
       <c r="H5">
-        <v>0.35</v>
+        <v>0.2178999930620193</v>
       </c>
       <c r="I5">
-        <v>0.35</v>
+        <v>0.2346999943256378</v>
       </c>
       <c r="J5">
-        <v>0.406</v>
+        <v>0.2154999971389771</v>
       </c>
       <c r="K5">
-        <v>0.6</v>
+        <v>0.2169000059366226</v>
       </c>
       <c r="L5">
-        <v>0.392</v>
-      </c>
-      <c r="M5">
-        <v>0.377</v>
-      </c>
-      <c r="N5">
-        <v>0.25</v>
-      </c>
-      <c r="O5">
-        <v>0.394</v>
-      </c>
-      <c r="P5">
-        <v>0.438</v>
-      </c>
-      <c r="Q5">
-        <v>0.448</v>
-      </c>
-      <c r="R5">
-        <v>0.346</v>
-      </c>
-      <c r="S5">
-        <v>0.462</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" t="s">
-        <v>360</v>
+        <v>0.2364999949932098</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6">
+        <v>0.2428999990224838</v>
+      </c>
+      <c r="C6">
+        <v>0.217399999499321</v>
       </c>
       <c r="D6">
-        <v>0.676</v>
+        <v>0.2027000039815903</v>
       </c>
       <c r="E6">
-        <v>0.641</v>
+        <v>0.1914000064134598</v>
       </c>
       <c r="F6">
-        <v>0.589</v>
+        <v>0.246299996972084</v>
+      </c>
+      <c r="G6">
+        <v>0.1605000048875809</v>
       </c>
       <c r="H6">
-        <v>0.421</v>
+        <v>0.1635999977588654</v>
       </c>
       <c r="I6">
-        <v>0.421</v>
+        <v>0.1588999927043915</v>
       </c>
       <c r="J6">
-        <v>0.622</v>
+        <v>0.1587000042200089</v>
       </c>
       <c r="K6">
-        <v>0.733</v>
+        <v>0.1697999984025955</v>
       </c>
       <c r="L6">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="M6">
-        <v>0.576</v>
-      </c>
-      <c r="N6">
-        <v>0.312</v>
-      </c>
-      <c r="O6">
-        <v>0.606</v>
-      </c>
-      <c r="P6">
-        <v>0.5</v>
-      </c>
-      <c r="Q6">
-        <v>0.667</v>
-      </c>
-      <c r="R6">
-        <v>0.513</v>
-      </c>
-      <c r="S6">
-        <v>0.615</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" t="s">
-        <v>255</v>
+        <v>0.1782000064849854</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7">
+        <v>0.2169999927282333</v>
+      </c>
+      <c r="C7">
+        <v>0.1732999980449677</v>
       </c>
       <c r="D7">
-        <v>0.791</v>
+        <v>0.1712999939918518</v>
       </c>
       <c r="E7">
-        <v>0.74</v>
+        <v>0.1797000020742416</v>
       </c>
       <c r="F7">
-        <v>0.666</v>
+        <v>0.1692000031471252</v>
       </c>
       <c r="G7">
-        <v>0.8139999999999999</v>
+        <v>0.1679999977350235</v>
       </c>
       <c r="H7">
-        <v>0.638</v>
+        <v>0.1684000045061111</v>
       </c>
       <c r="I7">
-        <v>0.638</v>
+        <v>0.1536999940872192</v>
       </c>
       <c r="J7">
-        <v>0.8179999999999999</v>
+        <v>0.1588999927043915</v>
       </c>
       <c r="K7">
-        <v>0.9330000000000001</v>
+        <v>0.1671999990940094</v>
       </c>
       <c r="L7">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="M7">
-        <v>0.856</v>
-      </c>
-      <c r="N7">
-        <v>0.625</v>
-      </c>
-      <c r="O7">
-        <v>0.434</v>
-      </c>
-      <c r="P7">
-        <v>0.344</v>
-      </c>
-      <c r="Q7">
-        <v>0.406</v>
-      </c>
-      <c r="R7">
-        <v>0.295</v>
-      </c>
-      <c r="S7">
-        <v>0.385</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
-      <c r="A8">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>357</v>
+        <v>0.1701000034809113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8">
+        <v>0.1229000017046928</v>
+      </c>
+      <c r="C8">
+        <v>0.1352999955415726</v>
       </c>
       <c r="D8">
-        <v>0.746</v>
+        <v>0.1326999962329865</v>
       </c>
       <c r="E8">
-        <v>0.6929999999999999</v>
+        <v>0.1118000000715256</v>
       </c>
       <c r="F8">
-        <v>0.614</v>
+        <v>0.1281999945640564</v>
       </c>
       <c r="G8">
-        <v>0.754</v>
+        <v>0.119999997317791</v>
       </c>
       <c r="H8">
-        <v>0.329</v>
+        <v>0.1247000023722649</v>
       </c>
       <c r="I8">
-        <v>0.329</v>
+        <v>0.1401000022888184</v>
       </c>
       <c r="J8">
-        <v>0.643</v>
+        <v>0.1218999996781349</v>
       </c>
       <c r="K8">
-        <v>0.767</v>
+        <v>0.1333999931812286</v>
       </c>
       <c r="L8">
-        <v>0.6</v>
-      </c>
-      <c r="M8">
-        <v>0.6820000000000001</v>
-      </c>
-      <c r="N8">
-        <v>0.438</v>
-      </c>
-      <c r="O8">
-        <v>0.535</v>
-      </c>
-      <c r="P8">
-        <v>0.469</v>
-      </c>
-      <c r="Q8">
-        <v>0.656</v>
-      </c>
-      <c r="R8">
-        <v>0.449</v>
-      </c>
-      <c r="S8">
-        <v>0.6919999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" t="s">
-        <v>358</v>
+        <v>0.1248999983072281</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9">
+        <v>0.1203000023961067</v>
+      </c>
+      <c r="C9">
+        <v>0.1048000007867813</v>
       </c>
       <c r="D9">
-        <v>0.8</v>
+        <v>0.1291999965906143</v>
       </c>
       <c r="E9">
-        <v>0.698</v>
+        <v>0.1298000067472458</v>
       </c>
       <c r="F9">
-        <v>0.547</v>
+        <v>0.1098000034689903</v>
       </c>
       <c r="G9">
-        <v>0.731</v>
+        <v>0.122699998319149</v>
       </c>
       <c r="H9">
-        <v>0.317</v>
+        <v>0.1264999955892563</v>
       </c>
       <c r="I9">
-        <v>0.317</v>
+        <v>0.1348000019788742</v>
       </c>
       <c r="J9">
-        <v>0.65</v>
+        <v>0.1187999993562698</v>
       </c>
       <c r="K9">
-        <v>0.6</v>
+        <v>0.1243999972939491</v>
       </c>
       <c r="L9">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="M9">
-        <v>0.627</v>
-      </c>
-      <c r="N9">
-        <v>0.438</v>
-      </c>
-      <c r="O9">
-        <v>0.475</v>
-      </c>
-      <c r="P9">
-        <v>0.406</v>
-      </c>
-      <c r="Q9">
-        <v>0.479</v>
-      </c>
-      <c r="R9">
-        <v>0.333</v>
-      </c>
-      <c r="S9">
-        <v>0.462</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>359</v>
+        <v>0.124600000679493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10">
+        <v>0.07699999958276749</v>
+      </c>
+      <c r="C10">
+        <v>0.09889999777078629</v>
       </c>
       <c r="D10">
-        <v>0.706</v>
+        <v>0.09539999812841415</v>
       </c>
       <c r="E10">
-        <v>0.634</v>
+        <v>0.09130000323057175</v>
       </c>
       <c r="F10">
-        <v>0.527</v>
+        <v>0.08470000326633453</v>
+      </c>
+      <c r="G10">
+        <v>0.1228000000119209</v>
       </c>
       <c r="H10">
-        <v>0.332</v>
+        <v>0.1365000009536743</v>
       </c>
       <c r="I10">
-        <v>0.332</v>
+        <v>0.154899999499321</v>
       </c>
       <c r="J10">
-        <v>0.51</v>
+        <v>0.1451999992132187</v>
       </c>
       <c r="K10">
-        <v>0.767</v>
+        <v>0.1371999979019165</v>
       </c>
       <c r="L10">
-        <v>0.458</v>
-      </c>
-      <c r="M10">
-        <v>0.483</v>
-      </c>
-      <c r="N10">
-        <v>0.438</v>
-      </c>
-      <c r="O10">
-        <v>0.535</v>
-      </c>
-      <c r="P10">
-        <v>0.656</v>
-      </c>
-      <c r="Q10">
-        <v>0.656</v>
-      </c>
-      <c r="R10">
-        <v>0.462</v>
-      </c>
-      <c r="S10">
-        <v>0.769</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" t="s">
-        <v>360</v>
+        <v>0.1216999962925911</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11">
+        <v>0.1014000028371811</v>
+      </c>
+      <c r="C11">
+        <v>0.1064999997615814</v>
       </c>
       <c r="D11">
-        <v>0.651</v>
+        <v>0.120899997651577</v>
       </c>
       <c r="E11">
-        <v>0.62</v>
+        <v>0.1089000031352043</v>
       </c>
       <c r="F11">
-        <v>0.575</v>
+        <v>0.08969999849796295</v>
+      </c>
+      <c r="G11">
+        <v>0.1103999987244606</v>
       </c>
       <c r="H11">
-        <v>0.341</v>
+        <v>0.1423999965190887</v>
       </c>
       <c r="I11">
-        <v>0.341</v>
+        <v>0.1238999962806702</v>
       </c>
       <c r="J11">
-        <v>0.5659999999999999</v>
+        <v>0.09960000216960907</v>
       </c>
       <c r="K11">
-        <v>0.667</v>
+        <v>0.09380000084638596</v>
       </c>
       <c r="L11">
-        <v>0.525</v>
-      </c>
-      <c r="M11">
-        <v>0.538</v>
-      </c>
-      <c r="N11">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="O11">
-        <v>0.505</v>
-      </c>
-      <c r="P11">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="Q11">
-        <v>0.74</v>
-      </c>
-      <c r="R11">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="S11">
-        <v>0.846</v>
+        <v>0.1123000010848045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12">
+        <v>0.09009999781847</v>
+      </c>
+      <c r="C12">
+        <v>0.09109999984502792</v>
+      </c>
+      <c r="D12">
+        <v>0.100100003182888</v>
+      </c>
+      <c r="E12">
+        <v>0.09650000184774399</v>
+      </c>
+      <c r="F12">
+        <v>0.09319999814033508</v>
+      </c>
+      <c r="G12">
+        <v>0.0885000005364418</v>
+      </c>
+      <c r="H12">
+        <v>0.07810000330209732</v>
+      </c>
+      <c r="I12">
+        <v>0.09040000289678574</v>
+      </c>
+      <c r="J12">
+        <v>0.08799999952316284</v>
+      </c>
+      <c r="K12">
+        <v>0.1055999994277954</v>
+      </c>
+      <c r="L12">
+        <v>0.09070000052452087</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13">
+        <v>0.08449999988079071</v>
+      </c>
+      <c r="C13">
+        <v>0.07890000194311142</v>
+      </c>
+      <c r="D13">
+        <v>0.08760000020265579</v>
+      </c>
+      <c r="E13">
+        <v>0.09260000288486481</v>
+      </c>
+      <c r="F13">
+        <v>0.08860000222921371</v>
+      </c>
+      <c r="G13">
+        <v>0.09529999643564224</v>
+      </c>
+      <c r="H13">
+        <v>0.09510000050067902</v>
+      </c>
+      <c r="I13">
+        <v>0.08470000326633453</v>
+      </c>
+      <c r="J13">
+        <v>0.09049999713897705</v>
+      </c>
+      <c r="K13">
+        <v>0.09440000355243683</v>
+      </c>
+      <c r="L13">
+        <v>0.09030000120401382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B14">
+        <v>0.09130000323057175</v>
+      </c>
+      <c r="C14">
+        <v>0.07760000228881836</v>
+      </c>
+      <c r="D14">
+        <v>0.1039000004529953</v>
+      </c>
+      <c r="E14">
+        <v>0.08380000293254852</v>
+      </c>
+      <c r="F14">
+        <v>0.1008000001311302</v>
+      </c>
+      <c r="G14">
+        <v>0.05820000171661377</v>
+      </c>
+      <c r="H14">
+        <v>0.06509999930858612</v>
+      </c>
+      <c r="I14">
+        <v>0.08079999685287476</v>
+      </c>
+      <c r="J14">
+        <v>0.06310000270605087</v>
+      </c>
+      <c r="K14">
+        <v>0.06989999860525131</v>
+      </c>
+      <c r="L14">
+        <v>0.07490000128746033</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15">
+        <v>0.06030000001192093</v>
+      </c>
+      <c r="C15">
+        <v>0.06679999828338623</v>
+      </c>
+      <c r="D15">
+        <v>0.07209999859333038</v>
+      </c>
+      <c r="E15">
+        <v>0.06830000132322311</v>
+      </c>
+      <c r="F15">
+        <v>0.06239999830722809</v>
+      </c>
+      <c r="G15">
+        <v>0.06289999932050705</v>
+      </c>
+      <c r="H15">
+        <v>0.0706000030040741</v>
+      </c>
+      <c r="I15">
+        <v>0.07819999754428864</v>
+      </c>
+      <c r="J15">
+        <v>0.05469999834895134</v>
+      </c>
+      <c r="K15">
+        <v>0.07029999792575836</v>
+      </c>
+      <c r="L15">
+        <v>0.06599999964237213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16">
+        <v>0.05009999871253967</v>
+      </c>
+      <c r="C16">
+        <v>0.05499999970197678</v>
+      </c>
+      <c r="D16">
+        <v>0.05469999834895134</v>
+      </c>
+      <c r="E16">
+        <v>0.05240000039339066</v>
+      </c>
+      <c r="F16">
+        <v>0.05169999971985817</v>
+      </c>
+      <c r="G16">
+        <v>0.05570000037550926</v>
+      </c>
+      <c r="H16">
+        <v>0.05880000069737434</v>
+      </c>
+      <c r="I16">
+        <v>0.05710000172257423</v>
+      </c>
+      <c r="J16">
+        <v>0.0568000003695488</v>
+      </c>
+      <c r="K16">
+        <v>0.05629999935626984</v>
+      </c>
+      <c r="L16">
+        <v>0.05539999902248383</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17">
+        <v>0.02859999984502792</v>
+      </c>
+      <c r="C17">
+        <v>0.02439999952912331</v>
+      </c>
+      <c r="D17">
+        <v>0.03009999915957451</v>
+      </c>
+      <c r="E17">
+        <v>0.02789999917149544</v>
+      </c>
+      <c r="F17">
+        <v>0.02769999951124191</v>
+      </c>
+      <c r="G17">
+        <v>0.02979999966919422</v>
+      </c>
+      <c r="H17">
+        <v>0.02730000019073486</v>
+      </c>
+      <c r="I17">
+        <v>0.02800000086426735</v>
+      </c>
+      <c r="J17">
+        <v>0.0296000000089407</v>
+      </c>
+      <c r="K17">
+        <v>0.02700000070035458</v>
+      </c>
+      <c r="L17">
+        <v>0.02859999984502792</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8734,688 +9500,175 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>2.88</v>
+      </c>
+      <c r="D2">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>21</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B3">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>3.16</v>
+      </c>
+      <c r="D3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>22</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B4">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>3.08</v>
+      </c>
+      <c r="D4">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>3.4</v>
+      </c>
+      <c r="D5">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B6">
         <v>25</v>
       </c>
-      <c r="H1" t="s">
+      <c r="C6">
+        <v>3.36</v>
+      </c>
+      <c r="D6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>3.08</v>
+      </c>
+      <c r="D7">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B8">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>3.12</v>
+      </c>
+      <c r="D8">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>3.12</v>
+      </c>
+      <c r="D9">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>28</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B10">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>3.04</v>
+      </c>
+      <c r="D10">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="L1" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B2">
-        <v>0.3815999925136566</v>
-      </c>
-      <c r="C2">
-        <v>0.4383000135421753</v>
-      </c>
-      <c r="D2">
-        <v>0.455700010061264</v>
-      </c>
-      <c r="E2">
-        <v>0.6923999786376953</v>
-      </c>
-      <c r="F2">
-        <v>0.4855999946594238</v>
-      </c>
-      <c r="G2">
-        <v>0.4767999947071075</v>
-      </c>
-      <c r="H2">
-        <v>0.4833000004291534</v>
-      </c>
-      <c r="I2">
-        <v>0.4679000079631805</v>
-      </c>
-      <c r="J2">
-        <v>0.4866000115871429</v>
-      </c>
-      <c r="K2">
-        <v>0.4801999926567078</v>
-      </c>
-      <c r="L2">
-        <v>0.5005999803543091</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B3">
-        <v>0.4943000078201294</v>
-      </c>
-      <c r="C3">
-        <v>0.4253000020980835</v>
-      </c>
-      <c r="D3">
-        <v>0.580299973487854</v>
-      </c>
-      <c r="E3">
-        <v>0.6037999987602234</v>
-      </c>
-      <c r="F3">
-        <v>0.4323999881744385</v>
-      </c>
-      <c r="G3">
-        <v>0.3041999936103821</v>
-      </c>
-      <c r="H3">
-        <v>0.3091000020503998</v>
-      </c>
-      <c r="I3">
-        <v>0.3553000092506409</v>
-      </c>
-      <c r="J3">
-        <v>0.3264999985694885</v>
-      </c>
-      <c r="K3">
-        <v>0.3519999980926514</v>
-      </c>
-      <c r="L3">
-        <v>0.4066999852657318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4">
-        <v>0.2639999985694885</v>
-      </c>
-      <c r="C4">
-        <v>0.2630000114440918</v>
-      </c>
-      <c r="D4">
-        <v>0.3093000054359436</v>
-      </c>
-      <c r="E4">
-        <v>0.2517000138759613</v>
-      </c>
-      <c r="F4">
-        <v>0.2382999956607819</v>
-      </c>
-      <c r="G4">
-        <v>0.226500004529953</v>
-      </c>
-      <c r="H4">
-        <v>0.214599996805191</v>
-      </c>
-      <c r="I4">
-        <v>0.2395000010728836</v>
-      </c>
-      <c r="J4">
-        <v>0.2134000062942505</v>
-      </c>
-      <c r="K4">
-        <v>0.2337000072002411</v>
-      </c>
-      <c r="L4">
-        <v>0.2398000061511993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5">
-        <v>0.2427999973297119</v>
-      </c>
-      <c r="C5">
-        <v>0.2456000000238419</v>
-      </c>
-      <c r="D5">
-        <v>0.301800012588501</v>
-      </c>
-      <c r="E5">
-        <v>0.2720000147819519</v>
-      </c>
-      <c r="F5">
-        <v>0.2520000040531158</v>
-      </c>
-      <c r="G5">
-        <v>0.2072000056505203</v>
-      </c>
-      <c r="H5">
-        <v>0.2178999930620193</v>
-      </c>
-      <c r="I5">
-        <v>0.2346999943256378</v>
-      </c>
-      <c r="J5">
-        <v>0.2154999971389771</v>
-      </c>
-      <c r="K5">
-        <v>0.2169000059366226</v>
-      </c>
-      <c r="L5">
-        <v>0.2364999949932098</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6">
-        <v>0.2428999990224838</v>
-      </c>
-      <c r="C6">
-        <v>0.217399999499321</v>
-      </c>
-      <c r="D6">
-        <v>0.2027000039815903</v>
-      </c>
-      <c r="E6">
-        <v>0.1914000064134598</v>
-      </c>
-      <c r="F6">
-        <v>0.246299996972084</v>
-      </c>
-      <c r="G6">
-        <v>0.1605000048875809</v>
-      </c>
-      <c r="H6">
-        <v>0.1635999977588654</v>
-      </c>
-      <c r="I6">
-        <v>0.1588999927043915</v>
-      </c>
-      <c r="J6">
-        <v>0.1587000042200089</v>
-      </c>
-      <c r="K6">
-        <v>0.1697999984025955</v>
-      </c>
-      <c r="L6">
-        <v>0.1782000064849854</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7">
-        <v>0.2169999927282333</v>
-      </c>
-      <c r="C7">
-        <v>0.1732999980449677</v>
-      </c>
-      <c r="D7">
-        <v>0.1712999939918518</v>
-      </c>
-      <c r="E7">
-        <v>0.1797000020742416</v>
-      </c>
-      <c r="F7">
-        <v>0.1692000031471252</v>
-      </c>
-      <c r="G7">
-        <v>0.1679999977350235</v>
-      </c>
-      <c r="H7">
-        <v>0.1684000045061111</v>
-      </c>
-      <c r="I7">
-        <v>0.1536999940872192</v>
-      </c>
-      <c r="J7">
-        <v>0.1588999927043915</v>
-      </c>
-      <c r="K7">
-        <v>0.1671999990940094</v>
-      </c>
-      <c r="L7">
-        <v>0.1701000034809113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8">
-        <v>0.1229000017046928</v>
-      </c>
-      <c r="C8">
-        <v>0.1352999955415726</v>
-      </c>
-      <c r="D8">
-        <v>0.1326999962329865</v>
-      </c>
-      <c r="E8">
-        <v>0.1118000000715256</v>
-      </c>
-      <c r="F8">
-        <v>0.1281999945640564</v>
-      </c>
-      <c r="G8">
-        <v>0.119999997317791</v>
-      </c>
-      <c r="H8">
-        <v>0.1247000023722649</v>
-      </c>
-      <c r="I8">
-        <v>0.1401000022888184</v>
-      </c>
-      <c r="J8">
-        <v>0.1218999996781349</v>
-      </c>
-      <c r="K8">
-        <v>0.1333999931812286</v>
-      </c>
-      <c r="L8">
-        <v>0.1248999983072281</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" t="s">
-        <v>73</v>
-      </c>
-      <c r="B9">
-        <v>0.1203000023961067</v>
-      </c>
-      <c r="C9">
-        <v>0.1048000007867813</v>
-      </c>
-      <c r="D9">
-        <v>0.1291999965906143</v>
-      </c>
-      <c r="E9">
-        <v>0.1298000067472458</v>
-      </c>
-      <c r="F9">
-        <v>0.1098000034689903</v>
-      </c>
-      <c r="G9">
-        <v>0.122699998319149</v>
-      </c>
-      <c r="H9">
-        <v>0.1264999955892563</v>
-      </c>
-      <c r="I9">
-        <v>0.1348000019788742</v>
-      </c>
-      <c r="J9">
-        <v>0.1187999993562698</v>
-      </c>
-      <c r="K9">
-        <v>0.1243999972939491</v>
-      </c>
-      <c r="L9">
-        <v>0.124600000679493</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10">
-        <v>0.07699999958276749</v>
-      </c>
-      <c r="C10">
-        <v>0.09889999777078629</v>
-      </c>
-      <c r="D10">
-        <v>0.09539999812841415</v>
-      </c>
-      <c r="E10">
-        <v>0.09130000323057175</v>
-      </c>
-      <c r="F10">
-        <v>0.08470000326633453</v>
-      </c>
-      <c r="G10">
-        <v>0.1228000000119209</v>
-      </c>
-      <c r="H10">
-        <v>0.1365000009536743</v>
-      </c>
-      <c r="I10">
-        <v>0.154899999499321</v>
-      </c>
-      <c r="J10">
-        <v>0.1451999992132187</v>
-      </c>
-      <c r="K10">
-        <v>0.1371999979019165</v>
-      </c>
-      <c r="L10">
-        <v>0.1216999962925911</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
       <c r="B11">
-        <v>0.1014000028371811</v>
+        <v>25</v>
       </c>
       <c r="C11">
-        <v>0.1064999997615814</v>
+        <v>2.96</v>
       </c>
       <c r="D11">
-        <v>0.120899997651577</v>
-      </c>
-      <c r="E11">
-        <v>0.1089000031352043</v>
-      </c>
-      <c r="F11">
-        <v>0.08969999849796295</v>
-      </c>
-      <c r="G11">
-        <v>0.1103999987244606</v>
-      </c>
-      <c r="H11">
-        <v>0.1423999965190887</v>
-      </c>
-      <c r="I11">
-        <v>0.1238999962806702</v>
-      </c>
-      <c r="J11">
-        <v>0.09960000216960907</v>
-      </c>
-      <c r="K11">
-        <v>0.09380000084638596</v>
-      </c>
-      <c r="L11">
-        <v>0.1123000010848045</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="B12">
-        <v>0.09009999781847</v>
+        <v>250</v>
       </c>
       <c r="C12">
-        <v>0.09109999984502792</v>
+        <v>3.12</v>
       </c>
       <c r="D12">
-        <v>0.100100003182888</v>
-      </c>
-      <c r="E12">
-        <v>0.09650000184774399</v>
-      </c>
-      <c r="F12">
-        <v>0.09319999814033508</v>
-      </c>
-      <c r="G12">
-        <v>0.0885000005364418</v>
-      </c>
-      <c r="H12">
-        <v>0.07810000330209732</v>
-      </c>
-      <c r="I12">
-        <v>0.09040000289678574</v>
-      </c>
-      <c r="J12">
-        <v>0.08799999952316284</v>
-      </c>
-      <c r="K12">
-        <v>0.1055999994277954</v>
-      </c>
-      <c r="L12">
-        <v>0.09070000052452087</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13">
-        <v>0.08449999988079071</v>
-      </c>
-      <c r="C13">
-        <v>0.07890000194311142</v>
-      </c>
-      <c r="D13">
-        <v>0.08760000020265579</v>
-      </c>
-      <c r="E13">
-        <v>0.09260000288486481</v>
-      </c>
-      <c r="F13">
-        <v>0.08860000222921371</v>
-      </c>
-      <c r="G13">
-        <v>0.09529999643564224</v>
-      </c>
-      <c r="H13">
-        <v>0.09510000050067902</v>
-      </c>
-      <c r="I13">
-        <v>0.08470000326633453</v>
-      </c>
-      <c r="J13">
-        <v>0.09049999713897705</v>
-      </c>
-      <c r="K13">
-        <v>0.09440000355243683</v>
-      </c>
-      <c r="L13">
-        <v>0.09030000120401382</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14">
-        <v>0.09130000323057175</v>
-      </c>
-      <c r="C14">
-        <v>0.07760000228881836</v>
-      </c>
-      <c r="D14">
-        <v>0.1039000004529953</v>
-      </c>
-      <c r="E14">
-        <v>0.08380000293254852</v>
-      </c>
-      <c r="F14">
-        <v>0.1008000001311302</v>
-      </c>
-      <c r="G14">
-        <v>0.05820000171661377</v>
-      </c>
-      <c r="H14">
-        <v>0.06509999930858612</v>
-      </c>
-      <c r="I14">
-        <v>0.08079999685287476</v>
-      </c>
-      <c r="J14">
-        <v>0.06310000270605087</v>
-      </c>
-      <c r="K14">
-        <v>0.06989999860525131</v>
-      </c>
-      <c r="L14">
-        <v>0.07490000128746033</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15">
-        <v>0.06030000001192093</v>
-      </c>
-      <c r="C15">
-        <v>0.06679999828338623</v>
-      </c>
-      <c r="D15">
-        <v>0.07209999859333038</v>
-      </c>
-      <c r="E15">
-        <v>0.06830000132322311</v>
-      </c>
-      <c r="F15">
-        <v>0.06239999830722809</v>
-      </c>
-      <c r="G15">
-        <v>0.06289999932050705</v>
-      </c>
-      <c r="H15">
-        <v>0.0706000030040741</v>
-      </c>
-      <c r="I15">
-        <v>0.07819999754428864</v>
-      </c>
-      <c r="J15">
-        <v>0.05469999834895134</v>
-      </c>
-      <c r="K15">
-        <v>0.07029999792575836</v>
-      </c>
-      <c r="L15">
-        <v>0.06599999964237213</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B16">
-        <v>0.05009999871253967</v>
-      </c>
-      <c r="C16">
-        <v>0.05499999970197678</v>
-      </c>
-      <c r="D16">
-        <v>0.05469999834895134</v>
-      </c>
-      <c r="E16">
-        <v>0.05240000039339066</v>
-      </c>
-      <c r="F16">
-        <v>0.05169999971985817</v>
-      </c>
-      <c r="G16">
-        <v>0.05570000037550926</v>
-      </c>
-      <c r="H16">
-        <v>0.05880000069737434</v>
-      </c>
-      <c r="I16">
-        <v>0.05710000172257423</v>
-      </c>
-      <c r="J16">
-        <v>0.0568000003695488</v>
-      </c>
-      <c r="K16">
-        <v>0.05629999935626984</v>
-      </c>
-      <c r="L16">
-        <v>0.05539999902248383</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12">
-      <c r="A17" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17">
-        <v>0.02859999984502792</v>
-      </c>
-      <c r="C17">
-        <v>0.02439999952912331</v>
-      </c>
-      <c r="D17">
-        <v>0.03009999915957451</v>
-      </c>
-      <c r="E17">
-        <v>0.02789999917149544</v>
-      </c>
-      <c r="F17">
-        <v>0.02769999951124191</v>
-      </c>
-      <c r="G17">
-        <v>0.02979999966919422</v>
-      </c>
-      <c r="H17">
-        <v>0.02730000019073486</v>
-      </c>
-      <c r="I17">
-        <v>0.02800000086426735</v>
-      </c>
-      <c r="J17">
-        <v>0.0296000000089407</v>
-      </c>
-      <c r="K17">
-        <v>0.02700000070035458</v>
-      </c>
-      <c r="L17">
-        <v>0.02859999984502792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12">
-      <c r="A18" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>0</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
